--- a/_business/商品进库表.xlsx
+++ b/_business/商品进库表.xlsx
@@ -1,56 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15800" windowWidth="28040" xWindow="4240" yWindow="640"/>
+    <workbookView windowWidth="21000" windowHeight="14280"/>
   </bookViews>
   <sheets>
-    <sheet name="2026二手商品进库表" sheetId="2" r:id="rId5"/>
+    <sheet name="2026二手商品进库表" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcMode="auto"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
-  <si>
-    <t xml:space="preserve">  </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>采购的耳机型号</t>
   </si>
@@ -103,6 +80,27 @@
     <t>黑*5白*1</t>
   </si>
   <si>
+    <t>SF0216541329217</t>
+  </si>
+  <si>
+    <t>15928</t>
+  </si>
+  <si>
+    <t>5月1日</t>
+  </si>
+  <si>
+    <t>邓雪梅</t>
+  </si>
+  <si>
+    <t>芳</t>
+  </si>
+  <si>
+    <t>方锦龙</t>
+  </si>
+  <si>
+    <t>5月6日</t>
+  </si>
+  <si>
     <t>freeclip仓</t>
   </si>
   <si>
@@ -133,45 +131,30 @@
     <t>蓝色仓进水可用*1</t>
   </si>
   <si>
-    <t>SF0216541329217</t>
-  </si>
-  <si>
-    <t>15928</t>
-  </si>
-  <si>
-    <t>5月1日</t>
-  </si>
-  <si>
-    <t>邓雪梅</t>
-  </si>
-  <si>
-    <t>芳</t>
-  </si>
-  <si>
-    <t>5月1日</t>
-  </si>
-  <si>
-    <t>方锦龙</t>
-  </si>
-  <si>
-    <t>5月6日</t>
-  </si>
-  <si>
-    <t>freebudspro3</t>
-  </si>
-  <si>
     <t>蓝仓蓝左白右</t>
   </si>
   <si>
+    <t>73600250729570</t>
+  </si>
+  <si>
+    <t>15929</t>
+  </si>
+  <si>
+    <t>婷婷</t>
+  </si>
+  <si>
+    <t>崔</t>
+  </si>
+  <si>
+    <t>5月4日</t>
+  </si>
+  <si>
     <t>freebuds6i</t>
   </si>
   <si>
     <t>白色</t>
   </si>
   <si>
-    <t>freebuds6i</t>
-  </si>
-  <si>
     <t>白色（缺右耳）</t>
   </si>
   <si>
@@ -184,9 +167,6 @@
     <t>freebudspro4</t>
   </si>
   <si>
-    <t>白色</t>
-  </si>
-  <si>
     <t>freebuds5仓</t>
   </si>
   <si>
@@ -199,12 +179,6 @@
     <t>freebudspro2</t>
   </si>
   <si>
-    <t>蓝色</t>
-  </si>
-  <si>
-    <t>freebudsse3</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -217,66 +191,21 @@
     <t>freebuds4e</t>
   </si>
   <si>
-    <t>白色</t>
-  </si>
-  <si>
     <t>freebudsse2</t>
   </si>
   <si>
     <t>紫色</t>
   </si>
   <si>
-    <t>二手</t>
-  </si>
-  <si>
-    <t>freebuds6i</t>
-  </si>
-  <si>
     <t>黑*1白*1紫*2</t>
   </si>
   <si>
-    <t>二手</t>
-  </si>
-  <si>
-    <t>73600250729570</t>
-  </si>
-  <si>
-    <t>15929</t>
-  </si>
-  <si>
-    <t>5月1日</t>
-  </si>
-  <si>
-    <t>婷婷</t>
-  </si>
-  <si>
-    <t>崔</t>
-  </si>
-  <si>
-    <t>5月1日</t>
-  </si>
-  <si>
-    <t>方锦龙</t>
-  </si>
-  <si>
-    <t>5月4日</t>
-  </si>
-  <si>
-    <t>freebudspro3</t>
-  </si>
-  <si>
     <t>绿色</t>
   </si>
   <si>
-    <t>freeclip</t>
-  </si>
-  <si>
     <t>紫仓黑色单耳</t>
   </si>
   <si>
-    <t>freebudspro4</t>
-  </si>
-  <si>
     <t>白仓黑色双耳</t>
   </si>
   <si>
@@ -292,12 +221,6 @@
     <t>银色</t>
   </si>
   <si>
-    <t>freebuds4e</t>
-  </si>
-  <si>
-    <t>银色</t>
-  </si>
-  <si>
     <t>freebuds4e耳</t>
   </si>
   <si>
@@ -310,31 +233,13 @@
     <t>freebuds4</t>
   </si>
   <si>
-    <t>白色</t>
-  </si>
-  <si>
-    <t>freebuds5</t>
-  </si>
-  <si>
-    <t>银色</t>
-  </si>
-  <si>
-    <t>freebudsse2</t>
-  </si>
-  <si>
     <t>黑*1蓝*1白*2</t>
   </si>
   <si>
-    <t>freebudsse2</t>
-  </si>
-  <si>
     <t>紫仓+黑左+黑右</t>
   </si>
   <si>
     <t>蓝仓+白左+白右</t>
-  </si>
-  <si>
-    <t>freebudsse2</t>
   </si>
   <si>
     <t>黑*5</t>
@@ -343,56 +248,393 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
-    <fill>
-      <patternFill patternType="none">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125">
-        <fgColor/>
-        <bgColor/>
-      </patternFill>
+  <fills count="35">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF0070C0"/>
-        <bgColor/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEBF1F8"/>
-        <bgColor/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -409,47 +651,333 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="true" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="true"/>
-    </xf>
-    <xf applyAlignment="true" applyBorder="false" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -498,7 +1026,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -531,26 +1059,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -583,23 +1094,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -741,93 +1235,81 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3 xr6 xr10 x15">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
-    <outlinePr summaryBelow="false" summaryRight="false"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="19"/>
+  <dimension ref="A1:O34"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" max="10" min="10" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="14" min="14" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="15" min="15" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" max="7" min="7" style="0" width="20"/>
+    <col min="1" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row customHeight="true" ht="29" r="1">
+    <row r="1" ht="29" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="1" t="s">
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="1:15">
+      <c r="A2" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row customHeight="true" ht="15" r="2">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="3">
@@ -839,22 +1321,38 @@
       <c r="F2" s="3">
         <v>3420</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="O2" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="3">
+    <row r="3" ht="15" customHeight="1" spans="1:15">
       <c r="A3" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6">
@@ -866,19 +1364,19 @@
       <c r="F3" s="6">
         <v>570</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+      <c r="N3" s="4"/>
       <c r="O3" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row customHeight="true" ht="15" r="4">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" spans="1:15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -891,8 +1389,8 @@
       <c r="F4" s="3">
         <v>-30</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -901,12 +1399,12 @@
       <c r="N4" s="4"/>
       <c r="O4" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="5">
+    <row r="5" ht="15" customHeight="1" spans="1:15">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="6">
@@ -918,20 +1416,20 @@
       <c r="F5" s="6">
         <v>1140</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
       <c r="O5" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="6">
+    <row r="6" ht="15" customHeight="1" spans="1:15">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="3">
@@ -943,8 +1441,8 @@
       <c r="F6" s="3">
         <v>1140</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -953,15 +1451,15 @@
       <c r="N6" s="4"/>
       <c r="O6" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="7">
+    <row r="7" ht="15" customHeight="1" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D7" s="6">
         <v>2</v>
@@ -972,19 +1470,19 @@
       <c r="F7" s="6">
         <v>600</v>
       </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
       <c r="O7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row customHeight="true" ht="15" r="8">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" spans="1:15">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -997,38 +1495,22 @@
       <c r="F8" s="3">
         <v>-30</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" spans="1:15">
+      <c r="A9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M8" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="O8" s="2"/>
-    </row>
-    <row customHeight="true" ht="15" r="9">
-      <c r="A9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>37</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="6">
@@ -1040,22 +1522,38 @@
       <c r="F9" s="6">
         <v>292</v>
       </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="G9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>39</v>
+      </c>
       <c r="O9" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="10">
+    <row r="10" ht="15" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="3">
@@ -1067,8 +1565,8 @@
       <c r="F10" s="3">
         <v>555</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -1077,12 +1575,12 @@
       <c r="N10" s="4"/>
       <c r="O10" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="11">
+    <row r="11" ht="15" customHeight="1" spans="1:15">
       <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="6">
@@ -1094,22 +1592,22 @@
       <c r="F11" s="6">
         <v>123</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
       <c r="O11" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="12">
+    <row r="12" ht="15" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="3">
@@ -1121,8 +1619,8 @@
       <c r="F12" s="3">
         <v>90</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1131,12 +1629,12 @@
       <c r="N12" s="4"/>
       <c r="O12" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="13">
+    <row r="13" ht="15" customHeight="1" spans="1:15">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="6">
@@ -1148,17 +1646,17 @@
       <c r="F13" s="6">
         <v>430</v>
       </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
       <c r="O13" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="14">
+    <row r="14" ht="15" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
         <v>46</v>
       </c>
@@ -1175,8 +1673,8 @@
       <c r="F14" s="3">
         <v>46</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -1187,12 +1685,12 @@
         <v>48</v>
       </c>
     </row>
-    <row customHeight="true" ht="15" r="15">
+    <row r="15" ht="15" customHeight="1" spans="1:15">
       <c r="A15" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="6">
@@ -1204,22 +1702,22 @@
       <c r="F15" s="6">
         <v>180</v>
       </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
       <c r="O15" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="16">
+    <row r="16" ht="15" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="3">
@@ -1231,8 +1729,8 @@
       <c r="F16" s="3">
         <v>360</v>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -1241,12 +1739,12 @@
       <c r="N16" s="4"/>
       <c r="O16" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="17">
+    <row r="17" ht="15" customHeight="1" spans="1:15">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="6">
@@ -1258,22 +1756,22 @@
       <c r="F17" s="6">
         <v>320</v>
       </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
       <c r="O17" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="18">
+    <row r="18" ht="15" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="3">
@@ -1285,8 +1783,8 @@
       <c r="F18" s="3">
         <v>130</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -1295,15 +1793,15 @@
       <c r="N18" s="4"/>
       <c r="O18" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="19">
+    <row r="19" ht="15" customHeight="1" spans="1:15">
       <c r="A19" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -1314,25 +1812,25 @@
       <c r="F19" s="6">
         <v>60</v>
       </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
       <c r="O19" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="20">
+    <row r="20" ht="15" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D20" s="3">
         <v>4</v>
@@ -1343,38 +1841,22 @@
       <c r="F20" s="3">
         <v>740</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="N20" s="4" t="s">
-        <v>70</v>
-      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
       <c r="O20" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="21">
+    <row r="21" ht="15" customHeight="1" spans="1:15">
       <c r="A21" s="5" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="6">
@@ -1396,12 +1878,12 @@
       <c r="N21" s="7"/>
       <c r="O21" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="22">
+    <row r="22" ht="15" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="3">
@@ -1423,12 +1905,12 @@
       <c r="N22" s="4"/>
       <c r="O22" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="23">
+    <row r="23" ht="15" customHeight="1" spans="1:15">
       <c r="A23" s="5" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="6">
@@ -1450,12 +1932,12 @@
       <c r="N23" s="7"/>
       <c r="O23" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="24">
+    <row r="24" ht="15" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="3">
@@ -1477,12 +1959,12 @@
       <c r="N24" s="4"/>
       <c r="O24" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="25">
+    <row r="25" ht="15" customHeight="1" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="6">
@@ -1504,12 +1986,12 @@
       <c r="N25" s="7"/>
       <c r="O25" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="26">
+    <row r="26" ht="15" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="3">
@@ -1531,12 +2013,12 @@
       <c r="N26" s="4"/>
       <c r="O26" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="27">
+    <row r="27" ht="15" customHeight="1" spans="1:15">
       <c r="A27" s="5" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="6">
@@ -1557,10 +2039,10 @@
       <c r="M27" s="7"/>
       <c r="N27" s="7"/>
       <c r="O27" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row customHeight="true" ht="15" r="28">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" spans="1:15">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -1583,12 +2065,12 @@
       <c r="N28" s="4"/>
       <c r="O28" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="29">
+    <row r="29" ht="15" customHeight="1" spans="1:15">
       <c r="A29" s="5" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="6">
@@ -1610,12 +2092,12 @@
       <c r="N29" s="7"/>
       <c r="O29" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="30">
+    <row r="30" ht="15" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="3">
@@ -1637,12 +2119,12 @@
       <c r="N30" s="4"/>
       <c r="O30" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="31">
+    <row r="31" ht="15" customHeight="1" spans="1:15">
       <c r="A31" s="5" t="s">
-        <v>90</v>
+        <v>54</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="6">
@@ -1664,12 +2146,12 @@
       <c r="N31" s="7"/>
       <c r="O31" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="32">
+    <row r="32" ht="15" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="3">
@@ -1691,10 +2173,10 @@
       <c r="N32" s="4"/>
       <c r="O32" s="2"/>
     </row>
-    <row customHeight="true" ht="15" r="33">
+    <row r="33" ht="15" customHeight="1" spans="1:15">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="6">
@@ -1716,12 +2198,12 @@
       <c r="N33" s="7"/>
       <c r="O33" s="5"/>
     </row>
-    <row customHeight="true" ht="15" r="34">
+    <row r="34" ht="15" customHeight="1" spans="1:15">
       <c r="A34" s="2" t="s">
-        <v>95</v>
+        <v>54</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="3">
@@ -1744,5 +2226,25 @@
       <c r="O34" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="G2:G8"/>
+    <mergeCell ref="G9:G20"/>
+    <mergeCell ref="H2:H8"/>
+    <mergeCell ref="H9:H20"/>
+    <mergeCell ref="I2:I8"/>
+    <mergeCell ref="I9:I20"/>
+    <mergeCell ref="J2:J8"/>
+    <mergeCell ref="J9:J20"/>
+    <mergeCell ref="K2:K8"/>
+    <mergeCell ref="K9:K20"/>
+    <mergeCell ref="L2:L8"/>
+    <mergeCell ref="L9:L20"/>
+    <mergeCell ref="M2:M8"/>
+    <mergeCell ref="M9:M20"/>
+    <mergeCell ref="N2:N8"/>
+    <mergeCell ref="N9:N20"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>